--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Sara Poppelaars</t>
+          <t>Sara Poppelaars, Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars, Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Sara Poppelaars</t>
+          <t>Sara Poppelaars, Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Sara Poppelaars</t>
+          <t>Sara Poppelaars, Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Sara Poppelaars</t>
+          <t>Sara Poppelaars, Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806379</v>
       </c>
       <c r="B2" t="n">
-        <v>57601</v>
+        <v>57614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806169</v>
       </c>
       <c r="B3" t="n">
-        <v>58448</v>
+        <v>58461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars, Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,7 +915,7 @@
         <v>136806168</v>
       </c>
       <c r="B4" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars, Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1031,7 +1031,7 @@
         <v>136806173</v>
       </c>
       <c r="B5" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars, Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806379</v>
       </c>
       <c r="B2" t="n">
-        <v>57614</v>
+        <v>57616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806169</v>
       </c>
       <c r="B3" t="n">
-        <v>58461</v>
+        <v>58463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806168</v>
       </c>
       <c r="B4" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806173</v>
       </c>
       <c r="B5" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806379</v>
       </c>
       <c r="B2" t="n">
-        <v>57616</v>
+        <v>57626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806169</v>
       </c>
       <c r="B3" t="n">
-        <v>58463</v>
+        <v>58473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806168</v>
       </c>
       <c r="B4" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806173</v>
       </c>
       <c r="B5" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806379</v>
       </c>
       <c r="B2" t="n">
-        <v>57626</v>
+        <v>57627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806169</v>
       </c>
       <c r="B3" t="n">
-        <v>58473</v>
+        <v>58474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806168</v>
       </c>
       <c r="B4" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806173</v>
       </c>
       <c r="B5" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36162-2026 artfynd.xlsx
+++ b/artfynd/A 36162-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136806169</v>
       </c>
       <c r="B3" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806168</v>
       </c>
       <c r="B4" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806173</v>
       </c>
       <c r="B5" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
